--- a/Block_F/Проверка A52.xlsx
+++ b/Block_F/Проверка A52.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sergey\OneDrive - МОСКОВСКИЙ ПОЛИТЕХНИЧЕСКИЙ УНИВЕРСИТЕТ\учёба\Крипта\2sem\Block_F\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4F8F1C-0237-4C5C-A804-8DC1D053C315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBEFCD9-1DDA-40AD-841C-C65337B44AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10245" yWindow="660" windowWidth="10365" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -402,7 +402,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1">
         <v>0</v>
@@ -411,7 +411,7 @@
         <v>1</v>
       </c>
       <c r="E1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -428,28 +428,28 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="3">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -457,56 +457,56 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -515,16 +515,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -532,7 +532,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -547,13 +547,13 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -567,7 +567,7 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -576,15 +576,15 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -599,21 +599,21 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -625,10 +625,10 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -636,7 +636,7 @@
     </row>
     <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -645,7 +645,7 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -654,27 +654,27 @@
         <v>7</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -691,10 +691,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -732,10 +732,10 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -746,13 +746,13 @@
         <v>0</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -769,7 +769,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -784,27 +784,27 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -813,10 +813,10 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -824,22 +824,22 @@
         <v>0</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>1</v>
@@ -847,36 +847,36 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -913,7 +913,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -922,10 +922,10 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21">
         <v>1</v>
@@ -933,7 +933,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -959,13 +959,13 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>1</v>
@@ -999,10 +999,10 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1013,13 +1013,13 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -1041,13 +1041,13 @@
         <v>1</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -1097,13 +1097,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="7:12" x14ac:dyDescent="0.25">
@@ -1139,13 +1139,13 @@
         <v>1</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="7:12" x14ac:dyDescent="0.25">
@@ -1167,10 +1167,10 @@
         <v>1</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -1184,10 +1184,10 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="7:12" x14ac:dyDescent="0.25">
@@ -1198,10 +1198,10 @@
         <v>1</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="7:12" x14ac:dyDescent="0.25">
@@ -1223,10 +1223,10 @@
         <v>1</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41">
         <v>1</v>
@@ -1237,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="7:12" x14ac:dyDescent="0.25">
@@ -1245,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="7:12" x14ac:dyDescent="0.25">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="7:12" x14ac:dyDescent="0.25">
@@ -1261,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="7:12" x14ac:dyDescent="0.25">
@@ -1269,7 +1269,7 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="7:12" x14ac:dyDescent="0.25">
@@ -1277,7 +1277,7 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="7:12" x14ac:dyDescent="0.25">
@@ -1293,7 +1293,7 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="7:10" x14ac:dyDescent="0.25">
@@ -1301,7 +1301,7 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="7:10" x14ac:dyDescent="0.25">
@@ -1317,7 +1317,7 @@
         <v>1</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="7:10" x14ac:dyDescent="0.25">
@@ -1341,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="7:10" x14ac:dyDescent="0.25">
@@ -1349,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="7:10" x14ac:dyDescent="0.25">
@@ -1365,7 +1365,7 @@
         <v>1</v>
       </c>
       <c r="J58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="7:10" x14ac:dyDescent="0.25">
@@ -1373,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="7:10" x14ac:dyDescent="0.25">
@@ -1397,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="7:10" x14ac:dyDescent="0.25">
@@ -1431,12 +1431,12 @@
     </row>
     <row r="67" spans="7:10" x14ac:dyDescent="0.25">
       <c r="J67">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="7:10" x14ac:dyDescent="0.25">
       <c r="J68">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="7:10" x14ac:dyDescent="0.25">
@@ -1456,17 +1456,17 @@
     </row>
     <row r="72" spans="7:10" x14ac:dyDescent="0.25">
       <c r="J72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="7:10" x14ac:dyDescent="0.25">
       <c r="J73">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="7:10" x14ac:dyDescent="0.25">
       <c r="J74">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="7:10" x14ac:dyDescent="0.25">
@@ -1481,12 +1481,12 @@
     </row>
     <row r="77" spans="7:10" x14ac:dyDescent="0.25">
       <c r="J77">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="7:10" x14ac:dyDescent="0.25">
       <c r="J78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="7:10" x14ac:dyDescent="0.25">
@@ -1496,7 +1496,7 @@
     </row>
     <row r="80" spans="7:10" x14ac:dyDescent="0.25">
       <c r="J80">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="10:10" x14ac:dyDescent="0.25">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="84" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="10:10" x14ac:dyDescent="0.25">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="86" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J86">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="10:10" x14ac:dyDescent="0.25">
@@ -1536,12 +1536,12 @@
     </row>
     <row r="88" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J89">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="10:10" x14ac:dyDescent="0.25">
@@ -1551,17 +1551,17 @@
     </row>
     <row r="91" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J91">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J92">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="10:10" x14ac:dyDescent="0.25">
@@ -1581,7 +1581,7 @@
     </row>
     <row r="97" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="10:10" x14ac:dyDescent="0.25">
@@ -1596,12 +1596,12 @@
     </row>
     <row r="100" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J100">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J101">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="10:10" x14ac:dyDescent="0.25">
@@ -1611,7 +1611,7 @@
     </row>
     <row r="103" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J103">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="10:10" x14ac:dyDescent="0.25">
@@ -1626,7 +1626,7 @@
     </row>
     <row r="106" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J106">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="10:10" x14ac:dyDescent="0.25">
@@ -1636,12 +1636,12 @@
     </row>
     <row r="108" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J108">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J109">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="10:10" x14ac:dyDescent="0.25">
@@ -1656,7 +1656,7 @@
     </row>
     <row r="112" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J112">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="10:10" x14ac:dyDescent="0.25">
@@ -1666,7 +1666,7 @@
     </row>
     <row r="114" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J114">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="10:10" x14ac:dyDescent="0.25">
